--- a/survey_templates/049_factors_influencing_academic_success--survey_templates.xlsx
+++ b/survey_templates/049_factors_influencing_academic_success--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Urban'}</t>
+          <t>Urban</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rural'}</t>
+          <t>Rural</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weak'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
